--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:09</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:00</t>
+    <t xml:space="preserve">2026-09-23 12:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13505</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:29</t>
+    <t xml:space="preserve">2026-10-02 13:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:52</t>
+    <t xml:space="preserve">2026-10-05 10:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -841,7 +841,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>995238.62</v>
+        <v>995238.63</v>
       </c>
     </row>
     <row r="15">
@@ -1198,7 +1198,7 @@
         <v>2020</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>754050.12</v>
+        <v>754050.13</v>
       </c>
     </row>
     <row r="36">
@@ -1249,7 +1249,7 @@
         <v>2020</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>720532.12</v>
+        <v>720532.13</v>
       </c>
     </row>
     <row r="39">
@@ -1266,7 +1266,7 @@
         <v>2020</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>719317.12</v>
+        <v>719317.13</v>
       </c>
     </row>
     <row r="40">
@@ -1351,7 +1351,7 @@
         <v>2020</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>702238.12</v>
+        <v>702238.13</v>
       </c>
     </row>
     <row r="45">
@@ -1402,7 +1402,7 @@
         <v>2020</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>687573.62</v>
+        <v>687573.63</v>
       </c>
     </row>
     <row r="48">
@@ -1487,7 +1487,7 @@
         <v>2020</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>595253.12</v>
+        <v>595253.13</v>
       </c>
     </row>
     <row r="53">
